--- a/data/trans_dic/IP24_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,76; 55,23</t>
+          <t>42,58; 62,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,32; 62,68</t>
+          <t>33,17; 51,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,27; 56,37</t>
+          <t>40,63; 54,78</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 28,26</t>
+          <t>11,08; 19,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 20,89</t>
+          <t>13,3; 22,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 22,24</t>
+          <t>13,1; 19,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 16,95</t>
+          <t>8,49; 16,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,55</t>
+          <t>8,4; 17,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,52</t>
+          <t>9,4; 15,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 49,07</t>
+          <t>10,15; 22,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 26,09</t>
+          <t>13,16; 21,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 34,52</t>
+          <t>12,67; 20,77</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25352</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>46657</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19464; 30929</t>
+          <t>20547; 29963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24784; 36710</t>
+          <t>16844; 26175</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48429; 64580</t>
+          <t>40238; 54249</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33644</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>49644</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25463; 45020</t>
+          <t>17407; 31069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21525; 38030</t>
+          <t>19356; 32964</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50409; 75926</t>
+          <t>39650; 59552</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49333</t>
+          <t>45874</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14360; 29329</t>
+          <t>16911; 33569</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19460; 39250</t>
+          <t>14669; 30962</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38591; 63543</t>
+          <t>35153; 57936</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>75515</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47461</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122976</t>
+          <t>85255</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47751; 135168</t>
+          <t>29698; 65907</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33820; 79700</t>
+          <t>33760; 56351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90361; 200561</t>
+          <t>69574; 114060</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>52,34%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42,14%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>42,58; 62,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33,17; 51,55</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40,63; 54,78</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>11,08; 19,77</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13,3; 22,65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13,1; 19,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8,49; 16,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8,4; 17,73</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 15,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,15; 22,52</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13,16; 21,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,67; 20,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>14,19; 20,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,46; 20,49</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15,43; 19,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.523381764250651</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4214435253820518</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4711149589247225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>25257</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21400</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46657</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4257837175206551</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3317116852198704</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4062922836135303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>20547; 29963</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16844; 26175</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40238; 54249</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6208983511809465</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5154683733848158</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5477662570295263</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1505873156167977</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1785167314076209</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1640147480802037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>23667</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25977</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49644</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1107606335415967</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1330115520820506</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1309974184713167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>17407; 31069</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>19356; 32964</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39650; 59552</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1976833443374846</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2265258055316165</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1967478725869566</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1226133268293156</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1228267784753117</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1227130607290508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>24420</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21454</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45874</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.08491129987812669</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.08398244093261679</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.09403350385271467</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>16911; 33569</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14669; 30962</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>35153; 57936</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1685518525494574</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.177258223742165</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1549761953670787</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1435201380121309</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1685986044303744</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1552353376469379</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>43254</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85255</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1014816507326163</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1315915917386749</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1266832244413368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>29698; 65907</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>33760; 56351</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69574; 114060</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2252128273396972</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2196454520342897</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2076849518589445</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1654325638349483</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1786179812462261</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1716783750878262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>115344</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>112087</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>227431</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1418564869991527</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1546355700538772</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1542568263708933</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>98906; 144738</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>97037; 128550</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>204352; 256861</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2075912977329456</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2048541522789729</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1938942446019938</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no realizan actividad física en su tiempo libre (o no tienen tiempo libre) (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>25257</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>21400</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>46657</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>20547</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>16844</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>40238</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>29963</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>26175</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>54249</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>23667</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>25977</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>49644</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17407</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>19356</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>39650</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>31069</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>32964</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>59552</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>24420</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>21454</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>45874</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>16911</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14669</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>35153</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>33569</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>30962</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>57936</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>43254</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>85255</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>29698</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>33760</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>69574</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>65907</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>56351</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>114060</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>186</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>115344</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>112087</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>227431</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>98906</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>97037</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>204352</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>144738</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>128550</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>256861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>